--- a/proveedores.xlsx
+++ b/proveedores.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4946"/>
+  <dimension ref="A1:D4953"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6158,7 +6158,7 @@
         <v>30707867120</v>
       </c>
       <c r="B412">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C412" t="str">
         <v/>
@@ -69440,6 +69440,9 @@
       <c r="B4932">
         <v>50</v>
       </c>
+      <c r="C4932" t="str">
+        <v/>
+      </c>
       <c r="D4932">
         <v>3</v>
       </c>
@@ -69451,6 +69454,9 @@
       <c r="B4933">
         <v>4</v>
       </c>
+      <c r="C4933" t="str">
+        <v/>
+      </c>
       <c r="D4933">
         <v>6</v>
       </c>
@@ -69462,6 +69468,9 @@
       <c r="B4934">
         <v>34</v>
       </c>
+      <c r="C4934" t="str">
+        <v/>
+      </c>
       <c r="D4934">
         <v>16</v>
       </c>
@@ -69473,6 +69482,9 @@
       <c r="B4935">
         <v>34</v>
       </c>
+      <c r="C4935" t="str">
+        <v/>
+      </c>
       <c r="D4935">
         <v>16</v>
       </c>
@@ -69484,6 +69496,9 @@
       <c r="B4936">
         <v>34</v>
       </c>
+      <c r="C4936" t="str">
+        <v/>
+      </c>
       <c r="D4936">
         <v>16</v>
       </c>
@@ -69495,6 +69510,9 @@
       <c r="B4937">
         <v>34</v>
       </c>
+      <c r="C4937" t="str">
+        <v/>
+      </c>
       <c r="D4937">
         <v>16</v>
       </c>
@@ -69506,6 +69524,9 @@
       <c r="B4938">
         <v>4</v>
       </c>
+      <c r="C4938" t="str">
+        <v/>
+      </c>
       <c r="D4938">
         <v>6</v>
       </c>
@@ -69517,6 +69538,9 @@
       <c r="B4939">
         <v>4</v>
       </c>
+      <c r="C4939" t="str">
+        <v/>
+      </c>
       <c r="D4939">
         <v>6</v>
       </c>
@@ -69528,6 +69552,9 @@
       <c r="B4940">
         <v>4</v>
       </c>
+      <c r="C4940" t="str">
+        <v/>
+      </c>
       <c r="D4940">
         <v>6</v>
       </c>
@@ -69539,6 +69566,9 @@
       <c r="B4941">
         <v>22</v>
       </c>
+      <c r="C4941" t="str">
+        <v/>
+      </c>
       <c r="D4941">
         <v>14</v>
       </c>
@@ -69550,6 +69580,9 @@
       <c r="B4942">
         <v>1</v>
       </c>
+      <c r="C4942" t="str">
+        <v/>
+      </c>
       <c r="D4942">
         <v>16</v>
       </c>
@@ -69561,6 +69594,9 @@
       <c r="B4943">
         <v>4</v>
       </c>
+      <c r="C4943" t="str">
+        <v/>
+      </c>
       <c r="D4943">
         <v>6</v>
       </c>
@@ -69572,6 +69608,9 @@
       <c r="B4944">
         <v>30</v>
       </c>
+      <c r="C4944" t="str">
+        <v/>
+      </c>
       <c r="D4944">
         <v>4</v>
       </c>
@@ -69583,6 +69622,9 @@
       <c r="B4945">
         <v>61</v>
       </c>
+      <c r="C4945" t="str">
+        <v/>
+      </c>
       <c r="D4945">
         <v>16</v>
       </c>
@@ -69594,13 +69636,93 @@
       <c r="B4946">
         <v>1</v>
       </c>
+      <c r="C4946" t="str">
+        <v/>
+      </c>
       <c r="D4946">
         <v>16</v>
       </c>
     </row>
+    <row r="4947">
+      <c r="A4947" t="str">
+        <v>30715666002</v>
+      </c>
+      <c r="B4947">
+        <v>12</v>
+      </c>
+      <c r="D4947">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4948">
+      <c r="A4948" t="str">
+        <v>30711923272</v>
+      </c>
+      <c r="B4948">
+        <v>24</v>
+      </c>
+      <c r="D4948">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4949">
+      <c r="A4949" t="str">
+        <v>27214146229</v>
+      </c>
+      <c r="B4949">
+        <v>1</v>
+      </c>
+      <c r="D4949">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4950">
+      <c r="A4950" t="str">
+        <v>20278555896</v>
+      </c>
+      <c r="B4950">
+        <v>4</v>
+      </c>
+      <c r="D4950">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4951">
+      <c r="A4951" t="str">
+        <v>20240801214</v>
+      </c>
+      <c r="B4951">
+        <v>4</v>
+      </c>
+      <c r="D4951">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4952">
+      <c r="A4952" t="str">
+        <v>30719215986</v>
+      </c>
+      <c r="B4952">
+        <v>5</v>
+      </c>
+      <c r="D4952">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4953">
+      <c r="A4953" t="str">
+        <v>20284529163</v>
+      </c>
+      <c r="B4953">
+        <v>4</v>
+      </c>
+      <c r="D4953">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4946"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4953"/>
   </ignoredErrors>
 </worksheet>
 </file>